--- a/live-exam-notifications/Live_Exam_Notifications.xlsx
+++ b/live-exam-notifications/Live_Exam_Notifications.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -87,8 +87,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +121,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D5D8C"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +163,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -215,6 +224,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -621,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B1:D20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="12" min="1" max="1"/>
@@ -641,7 +653,7 @@
     <row r="3" ht="15" customHeight="1" s="13">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 23 October 2026; refreshed automatically twice a week.</t>
+          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 24 October 2026; refreshed automatically twice a week.</t>
         </is>
       </c>
     </row>
@@ -672,7 +684,7 @@
     <row r="10" ht="15" customHeight="1" s="13">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Status reflects the position on 21 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
+          <t>Status reflects the position on 24 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
         </is>
       </c>
     </row>
@@ -756,9 +768,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B6:D7"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="B12:D13"/>
+    <mergeCell ref="B6:D7"/>
     <mergeCell ref="B8:D9"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -773,105 +785,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="14" customWidth="1" style="12" min="1" max="1"/>
-    <col width="30" customWidth="1" style="12" min="2" max="2"/>
-    <col width="40" customWidth="1" style="12" min="3" max="3"/>
-    <col width="14" customWidth="1" style="12" min="4" max="4"/>
-    <col width="34" customWidth="1" style="12" min="5" max="7"/>
-    <col width="9" customWidth="1" style="12" min="8" max="9"/>
-    <col width="30" customWidth="1" style="12" min="10" max="11"/>
-    <col width="14" customWidth="1" style="12" min="12" max="12"/>
-    <col width="16" customWidth="1" style="12" min="13" max="13"/>
-    <col width="30" customWidth="1" style="12" min="14" max="14"/>
-    <col width="12" customWidth="1" style="12" min="15" max="16"/>
-    <col width="40" customWidth="1" style="12" min="17" max="17"/>
+    <col width="20" customWidth="1" style="12" min="1" max="1"/>
+    <col width="20" customWidth="1" style="12" min="2" max="2"/>
+    <col width="20" customWidth="1" style="12" min="3" max="3"/>
+    <col width="20" customWidth="1" style="12" min="4" max="4"/>
+    <col width="20" customWidth="1" style="12" min="5" max="7"/>
+    <col width="20" customWidth="1" style="13" min="6" max="6"/>
+    <col width="20" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="12" min="8" max="9"/>
+    <col width="20" customWidth="1" style="13" min="9" max="9"/>
+    <col width="20" customWidth="1" style="12" min="10" max="11"/>
+    <col width="20" customWidth="1" style="13" min="11" max="11"/>
+    <col width="20" customWidth="1" style="12" min="12" max="12"/>
+    <col width="20" customWidth="1" style="12" min="13" max="13"/>
+    <col width="20" customWidth="1" style="12" min="14" max="14"/>
+    <col width="20" customWidth="1" style="12" min="15" max="16"/>
+    <col width="20" customWidth="1" style="13" min="16" max="16"/>
+    <col width="20" customWidth="1" style="12" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="13">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Conducting Body</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Notification</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Posts / Stream</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Age Limit (as notified)</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Age Min</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>Age Max</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>Age Relaxations</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>Application Window</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="L1" s="21" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="M1" s="21" t="inlineStr">
         <is>
           <t>Exam Date</t>
         </is>
       </c>
-      <c r="N1" s="20" t="inlineStr">
+      <c r="N1" s="21" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
       </c>
-      <c r="O1" s="20" t="inlineStr">
+      <c r="O1" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" s="20" t="inlineStr">
+      <c r="P1" s="21" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
       </c>
-      <c r="Q1" s="20" t="inlineStr">
+      <c r="Q1" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1509,32 +1526,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>approx. 1688 tentative posts (Pay Level 2 and Level 3)</t>
+          <t>1688 posts (Commercial Cum Ticket Clerk 700; Accounts Clerk cum Typist 200; Junior Clerk cum Typist 600; Trains Clerk 188)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10+2 (Intermediate) or equivalent (post-wise)</t>
+          <t>10+2 (Intermediate) or equivalent from a recognised Board (post-wise)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>not stated in sources consulted</t>
+          <t>Age (as on 01.01.2027): 18-30 years for UR/EWS (born not earlier than 02.01.1997 and not later than 01.01.2009)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>as per CEN (SC/ST/OBC-NCL/PwBD/ExSM relaxations)</t>
+          <t>SC/ST 5 years; OBC-NCL 3 years; PwBD 10/13/15 years; Ex-servicemen as per rules; others as per CEN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1564,12 +1581,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Indicative recruitment notice for CEN 07/2026; detailed notification to follow; opening and closing dates are tentative</t>
+          <t>Detailed CEN No. 07/2026 published 14-10-2026; fee Rs.500 (Rs.250 for SC/ST/ESM/PwBD/Female/Transgender/Minority/EBC); fee payment up to 15-11-2026; modification window 16-11-2026 to 25-11-2026</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3179,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>686 provisional vacancies (Deputy Tahsildar, Deputy MPDO, Senior Accountant, Assistant Section Officer, GST Officer etc.)</t>
+          <t>686 provisional vacancies (Deputy Tahsildar 200; Dy MPDO 176; Senior Accountant 90; Asst. Section Officer-GAD 71; Junior Accountant 48; GST Officer 40; Prohibition &amp; Excise SI 29; Asst. Registrar Co-op Societies 10; Sub-Registrar Gr-II 7; Municipal Commissioner Gr-III 6; ASO-Finance 5; ASO-Law 4)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3217,12 +3234,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Brief notification dated 13/10/2026; detailed notification with age, fee and community-wise breakup to follow</t>
+          <t>Brief notification dated 13/10/2026; detailed notification (with age limits, fee and community-wise breakup) due on or before 10/11/2026; screening test in offline OMR mode</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3875,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2721 tentative vacancies (SA 906, SGT 1205, SA Special Education 150, SGT Special Education 200, Principal 30, PGT 81, TGT 113, Physical Director 2, PET 34)</t>
+          <t>2,721 teacher posts (School Assistant 906; SGT 1,205; Special Education SA 150 and SGT 200; Societies/other managements 260: Principal 30, PGT 81, TGT 113, PD 2, PET 34)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3913,12 +3930,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Brief notification dated 13/10/2026; detailed notification with age limits, qualifications and dates to be available on or before 03.11.2026</t>
+          <t>Brief notification 13/10/2026; detailed notification (with age limits, qualifications and crucial dates) due on or before 03/11/2026; applications online only; Computer Based Test</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5322,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Indicative notice for CEN 08/2026 issued 21/10/2026; eligibility, age, fee and RRB-wise vacancies in the detailed CEN; Aadhaar verification required while applying</t>
+          <t>Indicative notice for CEN 08/2026 issued 21/10/2026; detailed CEN (with age, eligibility, fee and RRB-wise vacancies) expected 26/10/2026; apply tentatively 27/10/2026 to 25/11/2026; Aadhaar verification required while applying</t>
         </is>
       </c>
     </row>
@@ -5434,17 +5451,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>not stated in the brief notification; detailed notification published 16/10/2026</t>
+          <t>Minimum 18 years and maximum 30 years as on 01/07/2026 (detailed notification dated 16/10/2026)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5479,12 +5496,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; pay Rs.32,670-1,01,970</t>
+          <t>Detailed notification published 16/10/2026; 26 vacancies; age 18-30 as on 01/07/2026; pay Rs.32,670-1,01,970; online CBRT</t>
         </is>
       </c>
     </row>
@@ -5521,17 +5538,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>not stated in the brief notification; detailed notification published 16/10/2026</t>
+          <t>Minimum 25 years and maximum 44 years as on 01/07/2026 (detailed notification dated 16/10/2026)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5566,12 +5583,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; pay Rs.44,570-1,27,480; A.P. Juvenile Welfare Correctional Sub Service</t>
+          <t>Detailed notification published 16/10/2026; 15 vacancies; age 25-44 as on 01/07/2026; pay Rs.44,570-1,27,480; A.P. Juvenile Welfare Correctional Sub Service; online CBRT + CPT</t>
         </is>
       </c>
     </row>
@@ -5603,22 +5620,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bachelor's Degree (as prescribed in the detailed notification)</t>
+          <t>Bachelor's Degree in any branch of Engineering or Technology from a University recognised by the UGC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>not stated in the brief notification; detailed notification published 16/10/2026</t>
+          <t>Minimum 18 years and maximum 44 years as on 01/07/2026 (detailed notification dated 16/10/2026)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5653,12 +5670,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; pay Rs.54,060-1,40,540</t>
+          <t>Detailed notification published 16/10/2026; 78 vacancies; age 18-44 as on 01/07/2026; pay Rs.54,060-1,40,540; online CBRT + CPT</t>
         </is>
       </c>
     </row>
@@ -6094,6 +6111,963 @@
       <c r="Q61" t="inlineStr">
         <is>
           <t>NTA has invited online applications for NIFTEE-2027 for admissions to UG, PG, NLEA, Artisans and PhD programmes (NTA notice board, October 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Notification No. 09/2026 - Assistant Director, A.P. Economics &amp; Statistical Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 13/10/2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Detailed notification published 13/10/2026; age/qualification to be read from the notification; online CBRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Notification No. 14/2026 - Inspector of Factories, A.P. Factories Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 13/10/2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Online application opened 13/10/2026 (as per the Commission's notification)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Detailed notification published 13/10/2026; online application submission enabled from 13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Notification No. 15/2026 - Draughtsman Grade-II (Technical Assistant), A.P. Forest Subordinate Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 16/10/2026)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 16/10/2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>16/10/2026 to 05/11/2026 (as per the Commission's notification)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>05/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Detailed notification published 16/10/2026; A.P. Forest Subordinate Service; online CBRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Notification No. 21/2026 - Analyst Grade-II, A.P. Pollution Control Board (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 13/10/2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Online application submission enabled from 13/10/2026</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Detailed notification published 13/10/2026; A.P. Pollution Control Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Notification No. 22/2026 - English Reporters and Telugu Reporters, A.P. Legislature Services (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 13/10/2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Online application submission enabled from 13/10/2026</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Detailed notification published 13/10/2026; A.P. Legislature Secretariat Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Notification No. 26/2026 - Assistant Social Welfare Officer (A.P. Social Welfare Service) and Assistant Tribal Welfare Officer (A.P. Tribal Welfare Service)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 09/10/2026)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted; detailed notification published 09/10/2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Online application submission enabled from 09/10/2026</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Detailed notification published 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Notification No. 30/2026 - Senior Lecturer D.I.E.T, Lecturer S.C.E.R.T and Lecturer D.I.E.T, A.P. School Education Services</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>As prescribed in the detailed notification</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted (brief notification dated 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; as per AP State and Subordinate Service Rules</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>As per the Commission's notification (published 13/10/2026)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; detailed notification with age, fee and community-wise breakup to follow</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Indian Army</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Technical Entry Scheme (TES-57) - 10+2 Technical Entry Scheme, course commencing July 2027</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>90 provisional vacancies (unmarried male candidates)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10+2 (Class 12) with Physics, Chemistry and Mathematics, minimum 60% aggregate in PCM, and appeared in JEE (Main) 2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>16.5 to 19.5 years as on 01/07/2027 (born between 01 January 2008 and 01 January 2011, both dates inclusive)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>as per Government rules</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>14-10-2026 (1200 hrs) to 12-11-2026 (1200 hrs)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SSB interview (up to 5 days) tentatively February-March 2027</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://joinindianarmy.nic.in</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Permanent Commission entry; age is stated as a range (16.5-19.5 years, shown as 16-19 here as integers); 4-year training at CTW and IMA; selection via shortlisting on JEE (Main) and SSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Dr. NTR University of Health Sciences, Vijayawada</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Allied and Healthcare Courses 2026-27 (Competent Authority Quota) - Bachelor of Allied &amp; Healthcare, B.OT, B.Optom., BMLS, B.AOTT, B.RT, B.MRIT, B.DTT, B.RTT, B.PA etc.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>entrance-exam</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Admission to Allied and Healthcare degree courses (Competent Authority Quota) in colleges affiliated to Dr. NTR UHS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Passed Intermediate with the prescribed Science subjects (BiPC/MPC as specified for each course)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Minimum 17 years as on 31/12/2026; no upper age limit; candidates born on or after 01/01/2010 are not eligible</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>not applicable (no upper age limit)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>18-10-2026 (5:00 PM) to 28-10-2026 (5:00 PM)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Merit based on qualifying examination; counselling notified later</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://drntr.uhsap.in</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Notification dated 17/10/2026 (Endorsement No. 5359/EA5/Allied &amp; Healthcare Courses/CQ/2026-27); apply online only at apuhs/aptonline; fee Rs.2,500 (OC), Rs.2,000 (BC/SC/ST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dr. NTR University of Health Sciences, Vijayawada</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PG (Medical) Degree/Diploma Courses 2026-27 - Management Quota (MQ) admissions</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>entrance-exam</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Admission to PG (Medical) MD/MS/Diploma courses under Management Quota seats</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MBBS with NEET PG-2026 qualification and internship completed by 30-09-2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>as per NEET PG-2026 / NMC norms (not stated in the notification)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>as per rules</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Notification issued 17/10/2026 (schedule as per the MQ prospectus)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NEET PG-2026 based</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://drntr.uhsap.in</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>PG (Medical) MQ Prospectus and Notification 2026-27 published 17/10/2026; NEET PG-2026 cut-off percentiles apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NTA (for Ministry of Education)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SWAYAM-2026 (July Semester) Examination - 662 courses</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>entrance-exam</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SWAYAM online-course proctored examinations for 662 courses (July 2026 semester)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>As per the course enrolled for on the SWAYAM platform</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>No age limit prescribed</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>09-10-2026 to 31-10-2026 (up to 11:50 PM); fee payment up to 01-11-2026</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>08-12-2026 to 12-12-2026 (CBT)</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://exams.nta.nic.in/swayam/</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>NTA public notice dated 09/10/2026; correction window 02-11-2026 to 03-11-2026; exam duration 180 minutes</t>
         </is>
       </c>
     </row>

--- a/live-exam-notifications/Live_Exam_Notifications.xlsx
+++ b/live-exam-notifications/Live_Exam_Notifications.xlsx
@@ -163,7 +163,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -227,6 +227,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -633,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="12" min="1" max="1"/>
@@ -642,7 +645,6 @@
     <col width="12" customWidth="1" style="12" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="13">
       <c r="B2" s="14" t="inlineStr">
         <is>
@@ -653,11 +655,10 @@
     <row r="3" ht="15" customHeight="1" s="13">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 25 October 2026; refreshed automatically twice a week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 26 October 2026; refreshed automatically twice a week.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="15" customHeight="1" s="13">
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -684,7 +685,7 @@
     <row r="10" ht="15" customHeight="1" s="13">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Status reflects the position on 25 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
+          <t>Status reflects the position on 26 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
         </is>
       </c>
     </row>
@@ -697,7 +698,6 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="13"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="13">
       <c r="B15" s="16" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="12" min="1" max="1"/>
@@ -7072,263 +7072,1158 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>Central Govt</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>National Insurance Company Limited (NICL) - conducted through IBPS</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Recruitment of 321 Administrative Officers (Generalists &amp; Specialists) (Scale I), 2026-27</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>recruitment</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>321 vacancies (Generalist Officers 200; specialists 121 - Finance 20, Legal 20, IT 21, Automobile 10, Risk 28, Company Secretary 2, Agriculture 20)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>Graduation/PG with 60% (55% for SC/ST/PwBD); post-wise (CA/CMA, LL.B., B.E./B.Tech./MCA, Agriculture etc.)</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>21 to 30 years as on 01/10/2026 (born not earlier than 02/10/1996 and not later than 01/10/2005)</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="12" t="inlineStr">
         <is>
           <t>As per Government rules (SC/ST/OBC/PwBD/EWS/ExSM)</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="12" t="inlineStr">
         <is>
           <t>08/10/2026 to 28/10/2026</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L73" s="12" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M73" s="12" t="inlineStr">
         <is>
           <t>Phase-I 17/11/2026; Phase-II 22/12/2026</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="N73" s="12" t="inlineStr">
         <is>
           <t>https://ibpsreg.ibps.in/niiclsep26/</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" s="12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P73" s="12" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" s="12" t="inlineStr">
         <is>
           <t>Fee Rs.1,000 (Rs.250 for SC/ST/PwBD); basic pay Rs.82,485 per month. Notification dated 07/10/2026; registration through the IBPS portal (organisation code NICL). Prelims + Mains + Interview.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Central Govt</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>Indo-Tibetan Border Police Force (ITBP), Ministry of Home Affairs</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Recruitment of Meritorious Sportspersons to the post of Constable (General Duty) under Sports Quota-2025 (detailed advertisement dated 03/10/2026)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>recruitment</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>126 posts (72 male, 54 female) across 28 sports disciplines</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>Matriculation (10th pass) or equivalent, plus prescribed sports achievement between 01/01/2024 and 01/11/2026</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>18 to 23 years as on 01/11/2026</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="12" t="inlineStr">
         <is>
           <t>5 years (UR/EWS/OBC sportspersons), 8 years (OBC-NCL), 10 years (SC/ST); not open to PwBD or ex-servicemen</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="12" t="inlineStr">
         <is>
           <t>03/10/2026 to 01/11/2026 (11:59 PM)</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L74" s="12" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M74" s="12" t="inlineStr">
         <is>
           <t>Sports trials/documentation as per admit card</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N74" s="12" t="inlineStr">
         <is>
           <t>https://recruitment.itbpolice.nic.in</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O74" s="12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P74" s="12" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q74" s="12" t="inlineStr">
         <is>
           <t>Pay Level-3 (Rs.21,700-69,100); fee Rs.100 (male UR/OBC/EWS), exempt for women/SC/ST. Online only at recruitment.itbpolice.nic.in.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Central Govt</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>NTA (for Rashtriya Military Schools, Ministry of Defence)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>Rashtriya Military School Common Entrance Test (RMS CET) 2026 - admission to Class VI and IX (2027-28 session)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
         <is>
           <t>entrance-exam</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>Admission to Class VI and Class IX in the five Rashtriya Military Schools (Chail, Ajmer, Dholpur, Belgaum, Bengaluru)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>Class VI: passed/studying Class V; Class IX: passed Class VIII from a recognised school before admission</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>Class VI: 10 to 13 years as on 31 March of the year of admission; Class IX: 13 to 16 years</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="12" t="inlineStr">
         <is>
           <t>Six months relaxation in upper age limit for wards of personnel killed in action</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="12" t="inlineStr">
         <is>
           <t>23/09/2026 to 20/10/2026 (regular); late-fee window to 25/10/2026 (up to 5:00 PM)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L75" s="12" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M75" s="12" t="inlineStr">
         <is>
           <t>13/12/2026</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N75" s="12" t="inlineStr">
         <is>
           <t>https://exams.nta.nic.in/rmscet/</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="O75" s="12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P75" s="12" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="12" t="inlineStr">
         <is>
           <t>Regular window closed 20/10/2026; late submission with Rs.500 late fee open to 25/10/2026. Correction 27-28/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 10/2026 - Assistant Director, A.P. Tribal Welfare State Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Assistant Director in A.P. Tribal Welfare State Service (pay Rs 48,440 - 1,37,220)</t>
+        </is>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>1st or 2nd class Master's Degree in Social Anthropology / Sociology / Social Work from a recognised university, with at least two publications in national-level academic journals</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 13/10/2026); left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr"/>
+      <c r="I76" s="22" t="inlineStr"/>
+      <c r="J76" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K76" s="22" t="inlineStr">
+        <is>
+          <t>13/10/2026 to 02/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L76" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N76" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O76" s="22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P76" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q76" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 15/09/2026; single-level online CBRT only; detailed notification (vacancy break-up, age, community) was due on or before 13/10/2026 and is the crucial date for eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 11/2026 - Assistant Director (Forensic Engineering / Physics / Chemistry / Biology), A.P. State Forensic Science Laboratory Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>8 posts (Forensic Engineering 1 carried forward; Physics 2; Chemistry 2; Biology 3) - pay Rs 57,100 - 1,47,760</t>
+        </is>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>Forensic Engineering: B.E/B.Tech in Mechanical, Civil, Structural or Production Engineering; Physics: M.Sc (1st/2nd class) in Physics, Applied Physics, Material Science, Nuclear Physics, Electronics, Instrumentation, Nano Science/Technology or Geo Physics; Chemistry: M.Sc Chemistry or B.Sc with A.I.C. by examination in Forensic Sciences; Biology: M.Sc (1st/2nd class) in Botany/Zoology/Microbiology/Biochemistry/Genetics/Forensic Science. Exceptionally good eyesight (colour blindness a disqualification) and at least five years practical experience in a Forensic Science, Chemistry, Analytical or Police laboratory</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 06/10/2026); left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr"/>
+      <c r="I77" s="22" t="inlineStr"/>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K77" s="22" t="inlineStr">
+        <is>
+          <t>06/10/2026 to 27/10/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L77" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M77" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N77" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O77" s="22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P77" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q77" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 15/09/2026; applications close 27/10/2026; detailed notification (vacancy break-up, age, community) was due on or before 06/10/2026 and is the crucial date for eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 29/2026 - Deputy Commissioner of Endowments and Assistant Commissioner of Endowments, A.P. Charitable and Hindu Religious Institutions and Endowments Service</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>11 posts (Deputy Commissioner of Endowments 6 - Rs 65,360-1,54,980; Assistant Commissioner of Endowments 5 - Rs 48,440-1,37,220)</t>
+        </is>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>Practising advocate - Deputy Commissioner: at least 5 years' practice in the High Court of A.P. or the Supreme Court; Assistant Commissioner: advocate of the A.P. High Court for at least 3 years. Candidates must profess the Hindu religion (s.29(3), AP Charitable and Hindu Religious Institutions and Endowments Act, 1987)</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t>28-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="I78" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K78" s="22" t="inlineStr">
+        <is>
+          <t>02/11/2026 to 22/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L78" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N78" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O78" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P78" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q78" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 02/11/2026; BC-C and BC-E candidates are not eligible to the Endowments posts under the department special rules; detailed notification due on or before 02/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 31/2026 - Assistant Director (Mines), A.P. Mines and Geology Service</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Assistant Director (Mines), pay Rs 57,100 - 1,47,760</t>
+        </is>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>Degree in Mining Engineering from a recognised university, or Diploma in Mining Engineering from Indian School of Mines, Dhanbad or equivalent</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I79" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J79" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K79" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L79" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N79" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O79" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P79" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q79" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026 and is the crucial date for eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 32/2026 - Technical Assistant, A.P. Mines and Geology Sub-Service</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>36 provisional vacancies - Technical Assistant in A.P. Mines and Geology Sub-Service, pay Rs 35,570 - 1,09,910</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>B.Sc degree in Geology from a recognised university; practical experience of not less than one year in investigation of mineral deposits, geological mapping, mining or underground water resources preferred</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I80" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K80" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L80" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N80" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O80" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P80" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q80" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 33/2026 - Royalty Inspector, A.P. Mines and Geology Service</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>9 provisional vacancies - Royalty Inspector, pay Rs 45,830 - 1,30,580</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>Educational qualification will be given in the Detailed Notification, due on or before 06/11/2026</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I81" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J81" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K81" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L81" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N81" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O81" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P81" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q81" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; qualification and community break-up to be published in the detailed notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 34/2026 - Lab Assistant, A.P. Mining Subordinate Service</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Lab Assistant in A.P. Mining Subordinate Service, pay Rs 35,570 - 1,09,910</t>
+        </is>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>B.Sc degree with Chemistry from a university recognised by the UGC</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t>The brief notification fixes only the age reckoning date (01/07/2026) and defers the age range to the Detailed Notification - left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr"/>
+      <c r="I82" s="22" t="inlineStr"/>
+      <c r="J82" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K82" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L82" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N82" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O82" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P82" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q82" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; unlike the companion Mines notifications this one does not state the age range in the brief notice; detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 35/2026 - Assistant Chemical Examiner, A.P. Prohibition and Excise Subordinate Service</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>9 provisional vacancies - Assistant Chemical Examiner, pay Rs 40,970 - 1,24,380</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Science with Chemistry, or B.Sc (Pharmacy), from a recognised university or equivalent</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J83" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K83" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L83" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O83" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P83" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q83" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>Notification No. 36/2026 - Assistant Motor Vehicle Inspector, A.P. Transport Service</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>50 provisional vacancies - Assistant Motor Vehicle Inspector, pay Rs 48,440 - 1,37,220</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>Degree in Mechanical or Automobile Engineering, OR Diploma in Automobile Engineering from SBTET Andhra Pradesh / Technological Diploma Examination Board Hyderabad or equivalent; plus a motor driving licence with at least 3 years driving experience and a Heavy Transport Vehicle endorsement (2 years accepted where 3-year candidates are unavailable). Women holding only an LMV licence must acquire the HTV endorsement within two years of joining</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t>21-36 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I84" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="J84" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K84" s="22" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L84" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O84" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P84" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q84" s="22" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; physical requirements and community break-up to be given in the detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>NTA (for the Department of Higher Education, Ministry of Education)</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>Joint Entrance Examination (Main) - 2027, Session 1 (January 2027)</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>entrance-exam</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>Paper 1 (B.E./B.Tech) and Paper 2A (B.Arch) / 2B (B.Planning) - admission to NITs, IIITs and other centrally funded technical institutions, and the eligibility test for JEE (Advanced)</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>Pass in Class 12 (or equivalent) as per the JEE (Main) 2027 Information Bulletin - eligibility is fixed by the year of passing the qualifying examination</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr">
+        <is>
+          <t>No age range is prescribed in the public notice - eligibility for JEE (Main) 2027 is determined by the year of passing the Class 12 qualifying examination, so no numeric age limit is shown</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr"/>
+      <c r="I85" s="22" t="inlineStr"/>
+      <c r="J85" s="22" t="inlineStr">
+        <is>
+          <t>Not applicable - no age limit prescribed</t>
+        </is>
+      </c>
+      <c r="K85" s="22" t="inlineStr">
+        <is>
+          <t>24/10/2026 to 22/11/2026 (11:50 PM); late fee window 23/11/2026 to 26/11/2026; correction in particulars 27/11/2026 to 29/11/2026</t>
+        </is>
+      </c>
+      <c r="L85" s="22" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="M85" s="22" t="inlineStr">
+        <is>
+          <t>20, 21, 22, 23, 24 and 28 January 2027 (Session 1); city intimation slip 30/12/2026, admit cards from 13/01/2027</t>
+        </is>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>https://jeemain.nta.nic.in/</t>
+        </is>
+      </c>
+      <c r="O85" s="22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P85" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q85" s="22" t="inlineStr">
+        <is>
+          <t>Public notice dated 24/10/2026; Session 2 (April 2027) applications run 05/01/2027 to 03/02/2027 under a separate notice; the exam is held in 13 languages including Telugu; one application only per candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>UPSC</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Special Advertisement No. 51/2026 - Principal and Vice-Principal, Education Department, Government of NCT of Delhi</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>828 posts (Principal 124 - UR 69, EWS 11, OBC 18, SC 16, ST 10; Vice-Principal 704 - UR 287, EWS 71, OBC 189, SC 103, ST 54)</t>
+        </is>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t>Master's Degree and Bachelor of Education from a recognised university/institute. Principal: ten years' teaching experience as Vice-Principal/PGT/TGT in a recognised high/higher secondary school or college. Vice-Principal: two years as PGT or three years as TGT. Doctorate and administrative charge desirable</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t>Principal: 50 years for UR/EWS, 53 years for OBC and 55 years for SC/ST. Vice-Principal: 35 years for UR/EWS, 38 years for OBC and 40 years for SC/ST. Relaxable up to 10 years for PwBD subject to a maximum of 56 years</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr"/>
+      <c r="I86" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="J86" s="22" t="inlineStr">
+        <is>
+          <t>SC/ST 5 years; OBC 3 years; PwBD up to 10 years (maximum age 56); OBC reservation only against a certificate issued by the Government of NCT of Delhi</t>
+        </is>
+      </c>
+      <c r="K86" s="22" t="inlineStr">
+        <is>
+          <t>25/07/2026 to 14/08/2026, extended to 17/08/2026 (18:00 hrs); crucial date for age and eligibility remained 14/08/2026</t>
+        </is>
+      </c>
+      <c r="L86" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="M86" s="22" t="inlineStr">
+        <is>
+          <t>Pen-and-paper Combined Recruitment Test (CRT) on 01/11/2026 for shortlisting, followed by interview</t>
+        </is>
+      </c>
+      <c r="N86" s="22" t="inlineStr">
+        <is>
+          <t>https://www.upsc.gov.in/sites/default/files/AdvtNo-51-2026-Special-Engl-240726.pdf</t>
+        </is>
+      </c>
+      <c r="O86" s="22" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P86" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q86" s="22" t="inlineStr">
+        <is>
+          <t>Applications closed 17/08/2026; the shortlisting CRT is scheduled for 01/11/2026, so admit-card and exam-city notices are the live items to watch; max age shown is the Principal UR/EWS limit</t>
         </is>
       </c>
     </row>

--- a/live-exam-notifications/Live_Exam_Notifications.xlsx
+++ b/live-exam-notifications/Live_Exam_Notifications.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:D20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="12" min="1" max="1"/>
@@ -645,6 +645,7 @@
     <col width="12" customWidth="1" style="12" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="13">
       <c r="B2" s="14" t="inlineStr">
         <is>
@@ -655,10 +656,11 @@
     <row r="3" ht="15" customHeight="1" s="13">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 26 October 2026; refreshed automatically twice a week.</t>
-        </is>
-      </c>
-    </row>
+          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 27 October 2026; refreshed automatically twice a week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="13">
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -685,7 +687,7 @@
     <row r="10" ht="15" customHeight="1" s="13">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Status reflects the position on 26 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
+          <t>Status reflects the position on 27 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
         </is>
       </c>
     </row>
@@ -698,6 +700,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="13"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="13">
       <c r="B15" s="16" t="inlineStr">
         <is>
@@ -785,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="12" min="1" max="1"/>
@@ -2523,7 +2526,7 @@
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>14-12-2026 to 19-12-2026</t>
+          <t>14 to 18 December 2026 and 21 December 2026 (CBT), per NTA Examination Calendar for the December 2026 cycle published 26/10/2026</t>
         </is>
       </c>
       <c r="N20" s="12" t="inlineStr">
@@ -2538,12 +2541,12 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Fee Rs.1150 General; Rs.600 Gen-EWS/OBC-NCL; Rs.325 SC/ST/PwD/Third Gender; correction in particulars 02-11-2026 to 04-11-2026</t>
+          <t>Fee Rs.1150 General; Rs.600 Gen-EWS/OBC-NCL; Rs.325 SC/ST/PwD/Third Gender; correction in particulars 02-11-2026 to 04-11-2026; exam dates confirmed from NTA's Examination Calendar (December 2026 cycle onwards) published 26/10/2026</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3237,12 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
-          <t>Brief notification dated 13/10/2026; detailed notification (vacancy break-up, age, community, qualifications) due on or before 10/11/2026. Some aggregators quote 18-42, but this is not confirmed by any official detailed notification.</t>
+          <t>Brief notification dated 13/10/2026; online applications 10/11/2026 to 30/11/2026. The detailed notification (vacancy break-up, age, community, qualifications) has still not been hosted as on 27/10/2026 - the Commission's web note of 13/10/2026 says it will issue it on or before the start of applications, i.e. 10/11/2026. Age left blank rather than guessed; some aggregators quote 18-42, which no official detailed notification confirms</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4169,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>01/10/2026 to 26/10/2026 (extended to 10/11/2026)</t>
+          <t>01/10/2026 to 26/10/2026, extended till 10/11/2026 (11:59 PM) by Notification R.O.C.No.118/2026-RC dated 16/10/2026</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -4191,7 +4194,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr">
@@ -4253,7 +4256,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>30/09/2026 onwards (extended)</t>
+          <t>30/09/2026 onwards, extended till 10/11/2026 (5:00 PM) by Notification R.O.C.No.364/2026-RC dated 15/10/2026</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -4278,7 +4281,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr">
@@ -5379,7 +5382,7 @@
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>SC, ST, BC and EWS 5 years; PwBD 10 years; Ex-servicemen and NCC 3 years plus length of service; regular AP State Government employees up to 5 years; retrenched State Census Department employees 3 years</t>
+          <t>SC/ST/BC/EWS 5 years only. By Errata dated 23/10/2026 the age concessions for Ex-servicemen, whole-time NCC instructors, regular A.P. State Government employees and retrenched State Census Department employees do NOT apply to these posts, because Forest Section Officer and Forest Beat Officer are class-A posts under G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., dated 19/07/2000</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -5409,12 +5412,12 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; age 18-30 as on 01/07/2026; pay Rs.25,220-80,910</t>
+          <t>Detailed notification published 16/10/2026; age 18-30 as on 01/07/2026; pay Rs.25,220-80,910; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5469,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>SC, ST, BC and EWS 5 years; PwBD 10 years; Ex-servicemen and NCC 3 years plus length of service; regular AP State Government employees up to 5 years; retrenched State Census Department employees 3 years</t>
+          <t>SC/ST/BC/EWS 5 years only. By Errata dated 23/10/2026 the age concessions for Ex-servicemen, whole-time NCC instructors, regular A.P. State Government employees and retrenched State Census Department employees do NOT apply to these posts, because Forest Section Officer and Forest Beat Officer are class-A posts under G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., dated 19/07/2000</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -5496,12 +5499,12 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; 26 vacancies; age 18-30 as on 01/07/2026; pay Rs.32,670-1,01,970; online CBRT</t>
+          <t>Detailed notification published 16/10/2026; 26 vacancies; age 18-30 as on 01/07/2026; pay Rs.32,670-1,01,970; online CBRT; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6006,7 @@
       </c>
       <c r="M60" s="12" t="inlineStr">
         <is>
-          <t>December 2026 (as per the NTA schedule)</t>
+          <t>19, 22 and 27 December 2026, per NTA Examination Calendar for the December 2026 cycle published 26/10/2026</t>
         </is>
       </c>
       <c r="N60" s="12" t="inlineStr">
@@ -6018,12 +6021,12 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q60" s="12" t="inlineStr">
         <is>
-          <t>NTA has invited online applications for Joint CSIR-UGC NET December 2026; listed on the NTA notice board</t>
+          <t>NTA has invited online applications for Joint CSIR-UGC NET December 2026; listed on the NTA notice board; exam dates confirmed from NTA's Examination Calendar published 26/10/2026</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6093,7 @@
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>as per the NTA schedule</t>
+          <t>10 January 2027, per NTA Examination Calendar published 26/10/2026</t>
         </is>
       </c>
       <c r="N61" s="12" t="inlineStr">
@@ -6105,12 +6108,12 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q61" s="12" t="inlineStr">
         <is>
-          <t>NTA has invited online applications for NIFTEE-2027 for admissions to UG, PG, NLEA, Artisans and PhD programmes (NTA notice board, October 2026)</t>
+          <t>NTA has invited online applications for NIFTEE-2027 for admissions to UG, PG, NLEA, Artisans and PhD programmes (NTA notice board, October 2026); exam date confirmed from NTA's Examination Calendar published 26/10/2026</t>
         </is>
       </c>
     </row>
@@ -7368,8 +7371,16 @@
           <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 13/10/2026); left blank rather than guessed</t>
         </is>
       </c>
-      <c r="H76" s="22" t="inlineStr"/>
-      <c r="I76" s="22" t="inlineStr"/>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
       <c r="J76" s="22" t="inlineStr">
         <is>
           <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
@@ -7402,12 +7413,12 @@
       </c>
       <c r="P76" s="22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q76" s="22" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; single-level online CBRT only; detailed notification (vacancy break-up, age, community) was due on or before 13/10/2026 and is the crucial date for eligibility</t>
+          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 02/11/2026. The detailed notification was due on or before 13/10/2026 but had still not been hosted on the Commission's Recruitment Notifications page as on 27/10/2026, so the age clause is still unavailable and is left blank</t>
         </is>
       </c>
     </row>
@@ -7447,8 +7458,16 @@
           <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 06/10/2026); left blank rather than guessed</t>
         </is>
       </c>
-      <c r="H77" s="22" t="inlineStr"/>
-      <c r="I77" s="22" t="inlineStr"/>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
       <c r="J77" s="22" t="inlineStr">
         <is>
           <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
@@ -7481,12 +7500,12 @@
       </c>
       <c r="P77" s="22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q77" s="22" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; applications close 27/10/2026; detailed notification (vacancy break-up, age, community) was due on or before 06/10/2026 and is the crucial date for eligibility</t>
+          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 27/10/2026 (11:59 PM). The detailed notification had still not been hosted as on 27/10/2026, so the age clause is left blank - check the Commission's site before the window closes</t>
         </is>
       </c>
     </row>
@@ -7858,8 +7877,16 @@
           <t>The brief notification fixes only the age reckoning date (01/07/2026) and defers the age range to the Detailed Notification - left blank rather than guessed</t>
         </is>
       </c>
-      <c r="H82" s="22" t="inlineStr"/>
-      <c r="I82" s="22" t="inlineStr"/>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
       <c r="J82" s="22" t="inlineStr">
         <is>
           <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
@@ -7892,12 +7919,12 @@
       </c>
       <c r="P82" s="22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Q82" s="22" t="inlineStr">
         <is>
-          <t>Brief notification dated 13/10/2026; unlike the companion Mines notifications this one does not state the age range in the brief notice; detailed notification due on or before 06/11/2026</t>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026. The detailed notification is still not published as on 27/10/2026 - the brief notification states it will be available on or before 06/11/2026, so the age range remains blank</t>
         </is>
       </c>
     </row>
@@ -8103,8 +8130,16 @@
           <t>No age range is prescribed in the public notice - eligibility for JEE (Main) 2027 is determined by the year of passing the Class 12 qualifying examination, so no numeric age limit is shown</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr"/>
-      <c r="I85" s="22" t="inlineStr"/>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
       <c r="J85" s="22" t="inlineStr">
         <is>
           <t>Not applicable - no age limit prescribed</t>
@@ -8182,7 +8217,11 @@
           <t>Principal: 50 years for UR/EWS, 53 years for OBC and 55 years for SC/ST. Vice-Principal: 35 years for UR/EWS, 38 years for OBC and 40 years for SC/ST. Relaxable up to 10 years for PwBD subject to a maximum of 56 years</t>
         </is>
       </c>
-      <c r="H86" s="22" t="inlineStr"/>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
       <c r="I86" s="22" t="n">
         <v>55</v>
       </c>
@@ -8224,6 +8263,267 @@
       <c r="Q86" s="22" t="inlineStr">
         <is>
           <t>Applications closed 17/08/2026; the shortlisting CRT is scheduled for 01/11/2026, so admit-card and exam-city notices are the live items to watch; max age shown is the Principal UR/EWS limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>Rc.No.92/SLPRB/Rect.2/2026 - SCT Police Constables (Communications) (Men and Women)</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>200 provisional vacancies - Stipendiary Cadet Trainee Police Constable (Communications), Post Code No. 25</t>
+        </is>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>As on 01/07/2026: SSC plus an ITI certificate in Electronic Mechanic, Information Technology and Electronic System Maintenance, Computer Operator and Programming Assistant, Mechanic Consumer Electronics or Electrician; OR two-year Intermediate with MPC, or vocational Intermediate in EET (Electronic Engineering Technician) / ET (Electrical Technician) after SSC</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr">
+        <is>
+          <t>18-24 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/2002 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J87" s="22" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months as instructor); retrenched State Census Department temporary employees 3 years</t>
+        </is>
+      </c>
+      <c r="K87" s="22" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L87" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_COMM_Notification_2026.pdf</t>
+        </is>
+      </c>
+      <c r="O87" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P87" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q87" s="22" t="inlineStr">
+        <is>
+          <t>Detailed notification Rc.No.92/SLPRB/Rect.2/2026 dated 16/09/2026 issued under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026; online application and Preliminary Written Test dates to be notified separately by press release</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>Rc.No.93/SLPRB/Rect.2/2026 - SCT Police Constables (Mechanics) and (Drivers), Police Transport Organisation</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>213 provisional vacancies - SCT PC (Mechanics) (Men), Post Code No. 26: 15; SCT PC (Drivers) (Men), Post Code No. 27: 198</t>
+        </is>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>Post Code 26: SSC plus an ITI certificate in Wireman, Mechanic Motor Vehicle, Mechanic Diesel or Fitter. Post Code 27: Intermediate or its equivalent (or SSC plus an ITI certificate in Auto Electrician, Mechanic Motor Vehicle, Mechanic Diesel or Fitter), and a valid Light Motor Vehicle driving licence held continuously for at least two years as on the date of notification. Men only</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t>Post Code 26: 18-24 years as on 01/07/2026. Post Code 27: 18-27 years as on 01/07/2026. Serving A.P. Police Home Guards with 360 days of service in the preceding two years get an upper limit of 32 years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J88" s="22" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service; retrenched State Census Department employees 3 years</t>
+        </is>
+      </c>
+      <c r="K88" s="22" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L88" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M88" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_DRIVERANDMECHANIC_Notification_2026.pdf</t>
+        </is>
+      </c>
+      <c r="O88" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P88" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q88" s="22" t="inlineStr">
+        <is>
+          <t>Detailed notification Rc.No.93/SLPRB/Rect.2/2026 dated 16/09/2026; max age shown is the Post Code 27 limit (Post Code 26 is 18-24); online application and test dates to be notified separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>Rc.No.94/SLPRB/Rect.2/2026 - Driver Operator (Men) in State Disaster Response and Fire Services Department</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>147 provisional vacancies - Driver Operator (Men), Post Code No. 43, State Disaster Response and Fire Services Department</t>
+        </is>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>As on 01/07/2026: Intermediate or its equivalent recognised by the State Government, AND a correct and clear Heavy Transport Vehicle driving licence that has been valid for at least two years as on the date of the notification. Men only</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr">
+        <is>
+          <t>18-30 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/1996 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" s="22" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months); retrenched State Census Department temporary employees 3 years</t>
+        </is>
+      </c>
+      <c r="K89" s="22" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L89" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M89" s="22" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N89" s="22" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/DRIVER%20OPERATOR%20%20in%20Fire%20Services-%20Notification-%202026.pdf</t>
+        </is>
+      </c>
+      <c r="O89" s="22" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P89" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q89" s="22" t="inlineStr">
+        <is>
+          <t>Notification Rc.No.94/SLPRB/Rect.2/2026 dated 17/09/2026 under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026 (147 posts sanctioned); a corrigendum has also been issued; exact online application dates will be notified separately by press release</t>
         </is>
       </c>
     </row>

--- a/live-exam-notifications/Live_Exam_Notifications.xlsx
+++ b/live-exam-notifications/Live_Exam_Notifications.xlsx
@@ -656,7 +656,7 @@
     <row r="3" ht="15" customHeight="1" s="13">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 27 October 2026; refreshed automatically twice a week.</t>
+          <t>Currently open and recently closed recruitment and entrance-exam notifications, verified against official portals. Last verified 28 October 2026; refreshed automatically twice a week.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
     <row r="10" ht="15" customHeight="1" s="13">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Status reflects the position on 27 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
+          <t>Status reflects the position on 28 October 2026: green = open, blue = upcoming, grey = dates to be announced, red = recently closed.</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="12" min="1" max="1"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>Tier-I and Tier-II schedules to be notified later</t>
+          <t>Tier-I 30-11-2026 to 31-12-2026 (CBT); Tier-II to be notified</t>
         </is>
       </c>
       <c r="N5" s="12" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>Tier-I August-September 2026; Tier-II December 2026</t>
+          <t>Tier-I 30-09-2026 to 30-10-2026; Tier-II December 2026</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Fee Rs.850 plus GST (Rs.100 plus GST for SC/ST/PwBD); final result for Panel Year 2026</t>
+          <t>Fee Rs.850 plus GST (Rs.100 plus GST for SC/ST/PwBD); final result for Panel Year 2026 Final result of the General Cadre declared and published on the RBI website; no new Grade B cycle had been notified as on 28/10/2026.</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>06/10/2026 to 27/10/2026</t>
+          <t>06/10/2026 to 09/11/2026 (extended from 27/10/2026)</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>27/10/2026 (11:59 PM)</t>
+          <t>09/11/2026 (11:59 PM)</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Detailed notification dated 06/10/2026; vacancies revised upward from 163 to 166; screening in offline OMR mode, mains descriptive</t>
+          <t>Detailed notification dated 06/10/2026; vacancies revised upward from 163 to 166; screening in offline OMR mode, mains descriptive Applications extended by the Commission web note dated 27/10/2026 to 09/11/2026 (11:59 PM); no change in the Group-I screening test date. Screening Test date unchanged at 24/01/2027.</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>119 vacancies (96 by direct recruitment and 23 by recruitment by transfer)</t>
+          <t>119 posts (96 by Direct Recruitment and 23 by Recruitment by Transfer) in the A.P. State Judicial Service; pay scale Rs.77,840-1,36,520</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -4149,14 +4149,10 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Direct Recruitment: must not have completed 35 years as on 01/09/2026; Recruitment by Transfer: must not have completed 48 years as on 01/09/2026 (minimum age not specified)</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
+          <t>Below 35 years as on 01.09.2026 for Direct Recruitment; below 48 years as on 01.09.2026 for Recruitment by Transfer</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr"/>
       <c r="I39" s="12" t="inlineStr">
         <is>
           <t>35</t>
@@ -4164,12 +4160,12 @@
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>Direct Recruitment: SC/ST/BC/EWS 5 years; PwBD 10 years; service in the Defence forces of the Union is excluded while computing age. Recruitment by Transfer: only the 48-year limit is given, no further relaxation</t>
+          <t>5 years for SC/ST/BC/EWS and 10 years for persons with benchmark disabilities (upper age limit relaxed accordingly)</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>01/10/2026 to 26/10/2026, extended till 10/11/2026 (11:59 PM) by Notification R.O.C.No.118/2026-RC dated 16/10/2026</t>
+          <t>01-10-2026 to 10-11-2026 (extended from 26-10-2026)</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -4194,12 +4190,12 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>Notification No.118/2026-RC dated 25/09/2026; 119 vacancies (96 direct + 23 transfer); last date extended to 10/11/2026; fee Rs.1,500 (OC/EWS/BC), Rs.750 (SC/ST/PwBD); pay Rs.77,840-1,36,520; screening test + written exam + viva voce</t>
+          <t>Notification No.118/2026-RC dated 25/09/2026; 119 vacancies (96 direct + 23 transfer); last date extended to 10/11/2026; fee Rs.1,500 (OC/EWS/BC), Rs.750 (SC/ST/PwBD); pay Rs.77,840-1,36,520; screening test + written exam + viva voce Last date extended to 10/11/2026 (11:59 PM) by notification dated 16/10/2026; fee Rs.1,500 (OC/BC/EWS) and Rs.750 (SC/ST/PwBD).</t>
         </is>
       </c>
     </row>
@@ -5320,12 +5316,12 @@
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr">
@@ -5382,7 +5378,7 @@
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>SC/ST/BC/EWS 5 years only. By Errata dated 23/10/2026 the age concessions for Ex-servicemen, whole-time NCC instructors, regular A.P. State Government employees and retrenched State Census Department employees do NOT apply to these posts, because Forest Section Officer and Forest Beat Officer are class-A posts under G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., dated 19/07/2000</t>
+          <t>SC/ST/BC/EWS 5 years only. Errata dated 23/10/2026 removed the age concessions earlier printed at Sl.No.2-5 of para 5.2 for these Class-A posts: the Ex-servicemen, NCC instructor, regular A.P. State Government employee and retrenched census employee deductions no longer apply (G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., 19.07.2000).</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -5412,12 +5408,12 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; age 18-30 as on 01/07/2026; pay Rs.25,220-80,910; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn</t>
+          <t>Detailed notification published 16/10/2026; age 18-30 as on 01/07/2026; pay Rs.25,220-80,910; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn Errata to para 5.2 issued 23/10/2026 (age concessions for Ex-servicemen/NCC instructors/State Government employees/retrenched census employees withdrawn).</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5465,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>SC/ST/BC/EWS 5 years only. By Errata dated 23/10/2026 the age concessions for Ex-servicemen, whole-time NCC instructors, regular A.P. State Government employees and retrenched State Census Department employees do NOT apply to these posts, because Forest Section Officer and Forest Beat Officer are class-A posts under G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., dated 19/07/2000</t>
+          <t>SC/ST/BC/EWS 5 years only. Errata dated 23/10/2026 removed the age concessions earlier printed at Sl.No.2-5 of para 5.2 for these Class-A posts: the Ex-servicemen, NCC instructor, regular A.P. State Government employee and retrenched census employee deductions no longer apply (G.O.Ms.No.88, EFS&amp;T (For.IV) Dept., 19.07.2000).</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -5499,12 +5495,12 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr">
         <is>
-          <t>Detailed notification published 16/10/2026; 26 vacancies; age 18-30 as on 01/07/2026; pay Rs.32,670-1,01,970; online CBRT; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn</t>
+          <t>Detailed notification published 16/10/2026; 26 vacancies; age 18-30 as on 01/07/2026; pay Rs.32,670-1,01,970; online CBRT; Errata issued 23/10/2026 corrected Para 5.2 of the notification - only the SC/ST/BC/EWS 5-year relaxation survives, the ex-servicemen/NCC/State Government employee/census-employee concessions were notified in error and are withdrawn Errata to para 5.2 issued 23/10/2026 (age concessions for Ex-servicemen/NCC instructors/State Government employees/retrenched census employees withdrawn).</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5731,12 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>09/10/2026 to 29/10/2026 (11:59 PM)</t>
+          <t>09/10/2026 to 09/11/2026 (extended from 29/10/2026)</t>
         </is>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>29/10/2026 (11:59 PM)</t>
+          <t>09/11/2026 (11:59 PM)</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
@@ -5760,12 +5756,12 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; detailed notification dated 09/10/2026 (provisional vacancies raised from 73 to 97). Single-level CBRT plus qualifying Computer Proficiency Test.</t>
+          <t>Brief notification dated 15/09/2026; detailed notification dated 09/10/2026 (provisional vacancies raised from 73 to 97). Single-level CBRT plus qualifying Computer Proficiency Test. Applications extended by the Commission web note dated 27/10/2026 to 09/11/2026 (11:59 PM); no change in the Group-I screening test date.</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5818,12 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>06/10/2026 to 27/10/2026 (11:59 PM)</t>
+          <t>06/10/2026 to 09/11/2026 (extended from 27/10/2026)</t>
         </is>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>27/10/2026 (11:59 PM)</t>
+          <t>09/11/2026 (11:59 PM)</t>
         </is>
       </c>
       <c r="M58" s="12" t="inlineStr">
@@ -5847,12 +5843,12 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q58" s="12" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; detailed notification dated 06/10/2026 (41 vacancies incl. 01 carried-forward EWS). Pay Rs.57,100-1,47,760.</t>
+          <t>Brief notification dated 15/09/2026; detailed notification dated 06/10/2026 (41 vacancies incl. 01 carried-forward EWS). Pay Rs.57,100-1,47,760. Applications extended by the Commission web note dated 27/10/2026 to 09/11/2026 (11:59 PM); no change in the Group-I screening test date.</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5905,12 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>06/10/2026 to 27/10/2026 (11:59 PM)</t>
+          <t>06/10/2026 to 09/11/2026 (extended from 27/10/2026)</t>
         </is>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>27/10/2026 (11:59 PM)</t>
+          <t>09/11/2026 (11:59 PM)</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
@@ -5934,12 +5930,12 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q59" s="12" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; detailed notification dated 06/10/2026. Zonal post with 95% local reservation per the Presidential Order. Pay Rs.54,060-1,40,540.</t>
+          <t>Brief notification dated 15/09/2026; detailed notification dated 06/10/2026. Zonal post with 95% local reservation per the Presidential Order. Pay Rs.54,060-1,40,540. Applications extended by the Commission web note dated 27/10/2026 to 09/11/2026 (11:59 PM); no change in the Group-I screening test date.</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6002,7 @@
       </c>
       <c r="M60" s="12" t="inlineStr">
         <is>
-          <t>19, 22 and 27 December 2026, per NTA Examination Calendar for the December 2026 cycle published 26/10/2026</t>
+          <t>19, 22 and 27 December 2026 (CBT), per the NTA Examination Calendar published 26/10/2026</t>
         </is>
       </c>
       <c r="N60" s="12" t="inlineStr">
@@ -6021,12 +6017,12 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q60" s="12" t="inlineStr">
         <is>
-          <t>NTA has invited online applications for Joint CSIR-UGC NET December 2026; listed on the NTA notice board; exam dates confirmed from NTA's Examination Calendar published 26/10/2026</t>
+          <t>NTA has invited online applications for Joint CSIR-UGC NET December 2026; listed on the NTA notice board; exam dates confirmed from NTA's Examination Calendar published 26/10/2026 Exam dates revised by NTA on 26/10/2026 (earlier proposal was 20-21 December 2026).</t>
         </is>
       </c>
     </row>
@@ -6083,17 +6079,17 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>as per the NTA information bulletin</t>
+          <t>16-10-2026 to 16-11-2026 (late fee up to 21-11-2026)</t>
         </is>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>10 January 2027, per NTA Examination Calendar published 26/10/2026</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="N61" s="12" t="inlineStr">
@@ -6108,12 +6104,12 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q61" s="12" t="inlineStr">
         <is>
-          <t>NTA has invited online applications for NIFTEE-2027 for admissions to UG, PG, NLEA, Artisans and PhD programmes (NTA notice board, October 2026); exam date confirmed from NTA's Examination Calendar published 26/10/2026</t>
+          <t>NTA has invited online applications for NIFTEE-2027 for admissions to UG, PG, NLEA, Artisans and PhD programmes (NTA notice board, October 2026); exam date confirmed from NTA's Examination Calendar published 26/10/2026 Registration window and 10/01/2027 exam date confirmed from the NTA examination calendar published 26/10/2026.</t>
         </is>
       </c>
     </row>
@@ -6605,12 +6601,12 @@
       </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>09/10/2026 to 29/10/2026 (11:59 PM)</t>
+          <t>09/10/2026 to 09/11/2026 (extended from 29/10/2026)</t>
         </is>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>29/10/2026 (11:59 PM)</t>
+          <t>09/11/2026 (11:59 PM)</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
@@ -6630,12 +6626,12 @@
       </c>
       <c r="P67" s="12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Q67" s="12" t="inlineStr">
         <is>
-          <t>Brief notification dated 15/09/2026; detailed notification dated 09/10/2026. Pay Rs.48,440-1,37,220.</t>
+          <t>Brief notification dated 15/09/2026; detailed notification dated 09/10/2026. Pay Rs.48,440-1,37,220. Applications extended by the Commission web note dated 27/10/2026 to 09/11/2026 (11:59 PM); no change in the Group-I screening test date.</t>
         </is>
       </c>
     </row>
@@ -7321,1209 +7317,1559 @@
       </c>
       <c r="O75" s="12" t="inlineStr">
         <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q75" s="12" t="inlineStr">
+        <is>
+          <t>Regular window closed 20/10/2026; late submission with Rs.500 late fee open to 25/10/2026. Correction 27-28/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 10/2026 - Assistant Director, A.P. Tribal Welfare State Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Assistant Director in A.P. Tribal Welfare State Service (pay Rs 48,440 - 1,37,220)</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>1st or 2nd class Master's Degree in Social Anthropology / Sociology / Social Work from a recognised university, with at least two publications in national-level academic journals</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 13/10/2026); left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>13/10/2026 to 02/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L76" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="M76" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N76" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P75" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="Q75" s="12" t="inlineStr">
-        <is>
-          <t>Regular window closed 20/10/2026; late submission with Rs.500 late fee open to 25/10/2026. Correction 27-28/10/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q76" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 02/11/2026. The detailed notification was due on or before 13/10/2026 but had still not been hosted on the Commission's Recruitment Notifications page as on 27/10/2026, so the age clause is still unavailable and is left blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="B76" s="22" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>Andhra Pradesh Public Service Commission (APPSC)</t>
         </is>
       </c>
-      <c r="C76" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 10/2026 - Assistant Director, A.P. Tribal Welfare State Service (General Recruitment)</t>
-        </is>
-      </c>
-      <c r="D76" s="22" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 11/2026 - Assistant Director (Forensic Engineering / Physics / Chemistry / Biology), A.P. State Forensic Science Laboratory Service (General Recruitment)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>recruitment</t>
         </is>
       </c>
-      <c r="E76" s="22" t="inlineStr">
-        <is>
-          <t>1 provisional vacancy - Assistant Director in A.P. Tribal Welfare State Service (pay Rs 48,440 - 1,37,220)</t>
-        </is>
-      </c>
-      <c r="F76" s="22" t="inlineStr">
-        <is>
-          <t>1st or 2nd class Master's Degree in Social Anthropology / Sociology / Social Work from a recognised university, with at least two publications in national-level academic journals</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 13/10/2026); left blank rather than guessed</t>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>8 posts (Forensic Engineering 1 carried forward; Physics 2; Chemistry 2; Biology 3) - pay Rs 57,100 - 1,47,760</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Forensic Engineering: B.E/B.Tech in Mechanical, Civil, Structural or Production Engineering; Physics: M.Sc (1st/2nd class) in Physics, Applied Physics, Material Science, Nuclear Physics, Electronics, Instrumentation, Nano Science/Technology or Geo Physics; Chemistry: M.Sc Chemistry or B.Sc with A.I.C. by examination in Forensic Sciences; Biology: M.Sc (1st/2nd class) in Botany/Zoology/Microbiology/Biochemistry/Genetics/Forensic Science. Exceptionally good eyesight (colour blindness a disqualification) and at least five years practical experience in a Forensic Science, Chemistry, Analytical or Police laboratory</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 06/10/2026); left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="I76" s="22" t="inlineStr">
+      <c r="I77" s="12" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="J76" s="22" t="inlineStr">
+      <c r="J77" s="12" t="inlineStr">
         <is>
           <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
         </is>
       </c>
-      <c r="K76" s="22" t="inlineStr">
-        <is>
-          <t>13/10/2026 to 02/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L76" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="M76" s="22" t="inlineStr">
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>06/10/2026 to 27/10/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M77" s="12" t="inlineStr">
         <is>
           <t>tba (single-level CBRT, no screening test)</t>
         </is>
       </c>
-      <c r="N76" s="22" t="inlineStr">
+      <c r="N77" s="12" t="inlineStr">
         <is>
           <t>https://psc.ap.gov.in</t>
         </is>
       </c>
-      <c r="O76" s="22" t="inlineStr">
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 27/10/2026 (11:59 PM). The detailed notification had still not been hosted as on 27/10/2026, so the age clause is left blank - check the Commission's site before the window closes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 29/2026 - Deputy Commissioner of Endowments and Assistant Commissioner of Endowments, A.P. Charitable and Hindu Religious Institutions and Endowments Service</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>11 posts (Deputy Commissioner of Endowments 6 - Rs 65,360-1,54,980; Assistant Commissioner of Endowments 5 - Rs 48,440-1,37,220)</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Practising advocate - Deputy Commissioner: at least 5 years' practice in the High Court of A.P. or the Supreme Court; Assistant Commissioner: advocate of the A.P. High Court for at least 3 years. Candidates must profess the Hindu religion (s.29(3), AP Charitable and Hindu Religious Institutions and Endowments Act, 1987)</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>28-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>02/11/2026 to 22/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L78" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="M78" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N78" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q78" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 02/11/2026; BC-C and BC-E candidates are not eligible to the Endowments posts under the department special rules; detailed notification due on or before 02/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 31/2026 - Assistant Director (Mines), A.P. Mines and Geology Service</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Assistant Director (Mines), pay Rs 57,100 - 1,47,760</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Degree in Mining Engineering from a recognised university, or Diploma in Mining Engineering from Indian School of Mines, Dhanbad or equivalent</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N79" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026 and is the crucial date for eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 32/2026 - Technical Assistant, A.P. Mines and Geology Sub-Service</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>36 provisional vacancies - Technical Assistant in A.P. Mines and Geology Sub-Service, pay Rs 35,570 - 1,09,910</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>B.Sc degree in Geology from a recognised university; practical experience of not less than one year in investigation of mineral deposits, geological mapping, mining or underground water resources preferred</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L80" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M80" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N80" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q80" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 33/2026 - Royalty Inspector, A.P. Mines and Geology Service</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>9 provisional vacancies - Royalty Inspector, pay Rs 45,830 - 1,30,580</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Educational qualification will be given in the Detailed Notification, due on or before 06/11/2026</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N81" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; qualification and community break-up to be published in the detailed notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 34/2026 - Lab Assistant, A.P. Mining Subordinate Service</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>1 provisional vacancy - Lab Assistant in A.P. Mining Subordinate Service, pay Rs 35,570 - 1,09,910</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>B.Sc degree with Chemistry from a university recognised by the UGC</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>The brief notification fixes only the age reckoning date (01/07/2026) and defers the age range to the Detailed Notification - left blank rather than guessed</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L82" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M82" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N82" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q82" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026. The detailed notification is still not published as on 27/10/2026 - the brief notification states it will be available on or before 06/11/2026, so the age range remains blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 35/2026 - Assistant Chemical Examiner, A.P. Prohibition and Excise Subordinate Service</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>9 provisional vacancies - Assistant Chemical Examiner, pay Rs 40,970 - 1,24,380</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Science with Chemistry, or B.Sc (Pharmacy), from a recognised university or equivalent</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>18-44 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Notification No. 36/2026 - Assistant Motor Vehicle Inspector, A.P. Transport Service</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>50 provisional vacancies - Assistant Motor Vehicle Inspector, pay Rs 48,440 - 1,37,220</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Degree in Mechanical or Automobile Engineering, OR Diploma in Automobile Engineering from SBTET Andhra Pradesh / Technological Diploma Examination Board Hyderabad or equivalent; plus a motor driving licence with at least 3 years driving experience and a Heavy Transport Vehicle endorsement (2 years accepted where 3-year candidates are unavailable). Women holding only an LMV licence must acquire the HTV endorsement within two years of joining</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>21-36 years (Age as on 01/07/2026)</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr">
+        <is>
+          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="L84" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="M84" s="12" t="inlineStr">
+        <is>
+          <t>tba (single-level CBRT, no screening test)</t>
+        </is>
+      </c>
+      <c r="N84" s="12" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P84" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q84" s="12" t="inlineStr">
+        <is>
+          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; physical requirements and community break-up to be given in the detailed notification due on or before 06/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>NTA (for the Department of Higher Education, Ministry of Education)</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Joint Entrance Examination (Main) - 2027, Session 1 (January 2027)</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>entrance-exam</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Paper 1 (B.E./B.Tech) and Paper 2A (B.Arch) / 2B (B.Planning) - admission to NITs, IIITs and other centrally funded technical institutions, and the eligibility test for JEE (Advanced)</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Pass in Class 12 (or equivalent) as per the JEE (Main) 2027 Information Bulletin - eligibility is fixed by the year of passing the qualifying examination</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>No age range is prescribed in the public notice - eligibility for JEE (Main) 2027 is determined by the year of passing the Class 12 qualifying examination, so no numeric age limit is shown</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>Not applicable - no age limit prescribed</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>24/10/2026 to 22/11/2026 (11:50 PM); late fee window 23/11/2026 to 26/11/2026; correction in particulars 27/11/2026 to 29/11/2026</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>20, 21, 22, 23, 24 and 28 January 2027 (Session 1); city intimation slip 30/12/2026, admit cards from 13/01/2027</t>
+        </is>
+      </c>
+      <c r="N85" s="12" t="inlineStr">
+        <is>
+          <t>https://jeemain.nta.nic.in/</t>
+        </is>
+      </c>
+      <c r="O85" s="12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P76" s="22" t="inlineStr">
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="inlineStr">
+        <is>
+          <t>Public notice dated 24/10/2026; Session 2 (April 2027) applications run 05/01/2027 to 03/02/2027 under a separate notice; the exam is held in 13 languages including Telugu; one application only per candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>UPSC</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Special Advertisement No. 51/2026 - Principal and Vice-Principal, Education Department, Government of NCT of Delhi</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>828 posts (Principal 124 - UR 69, EWS 11, OBC 18, SC 16, ST 10; Vice-Principal 704 - UR 287, EWS 71, OBC 189, SC 103, ST 54)</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Master's Degree and Bachelor of Education from a recognised university/institute. Principal: ten years' teaching experience as Vice-Principal/PGT/TGT in a recognised high/higher secondary school or college. Vice-Principal: two years as PGT or three years as TGT. Doctorate and administrative charge desirable</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>Principal: 50 years for UR/EWS, 53 years for OBC and 55 years for SC/ST. Vice-Principal: 35 years for UR/EWS, 38 years for OBC and 40 years for SC/ST. Relaxable up to 10 years for PwBD subject to a maximum of 56 years</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST 5 years; OBC 3 years; PwBD up to 10 years (maximum age 56); OBC reservation only against a certificate issued by the Government of NCT of Delhi</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>25/07/2026 to 14/08/2026, extended to 17/08/2026 (18:00 hrs); crucial date for age and eligibility remained 14/08/2026</t>
+        </is>
+      </c>
+      <c r="L86" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="M86" s="12" t="inlineStr">
+        <is>
+          <t>Pen-and-paper Combined Recruitment Test (CRT) on 01/11/2026 for shortlisting, followed by interview</t>
+        </is>
+      </c>
+      <c r="N86" s="12" t="inlineStr">
+        <is>
+          <t>https://www.upsc.gov.in/sites/default/files/AdvtNo-51-2026-Special-Engl-240726.pdf</t>
+        </is>
+      </c>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q86" s="12" t="inlineStr">
+        <is>
+          <t>Applications closed 17/08/2026; the shortlisting CRT is scheduled for 01/11/2026, so admit-card and exam-city notices are the live items to watch; max age shown is the Principal UR/EWS limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Rc.No.92/SLPRB/Rect.2/2026 - SCT Police Constables (Communications) (Men and Women)</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>200 provisional vacancies - Stipendiary Cadet Trainee Police Constable (Communications), Post Code No. 25</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>As on 01/07/2026: SSC plus an ITI certificate in Electronic Mechanic, Information Technology and Electronic System Maintenance, Computer Operator and Programming Assistant, Mechanic Consumer Electronics or Electrician; OR two-year Intermediate with MPC, or vocational Intermediate in EET (Electronic Engineering Technician) / ET (Electrical Technician) after SSC</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>18-24 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/2002 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months as instructor); retrenched State Census Department temporary employees 3 years</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N87" s="12" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_COMM_Notification_2026.pdf</t>
+        </is>
+      </c>
+      <c r="O87" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="Q76" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 02/11/2026. The detailed notification was due on or before 13/10/2026 but had still not been hosted on the Commission's Recruitment Notifications page as on 27/10/2026, so the age clause is still unavailable and is left blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="Q87" s="12" t="inlineStr">
+        <is>
+          <t>Detailed notification Rc.No.92/SLPRB/Rect.2/2026 dated 16/09/2026 issued under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026; online application and Preliminary Written Test dates to be notified separately by press release</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 11/2026 - Assistant Director (Forensic Engineering / Physics / Chemistry / Biology), A.P. State Forensic Science Laboratory Service (General Recruitment)</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Rc.No.93/SLPRB/Rect.2/2026 - SCT Police Constables (Mechanics) and (Drivers), Police Transport Organisation</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>recruitment</t>
         </is>
       </c>
-      <c r="E77" s="22" t="inlineStr">
-        <is>
-          <t>8 posts (Forensic Engineering 1 carried forward; Physics 2; Chemistry 2; Biology 3) - pay Rs 57,100 - 1,47,760</t>
-        </is>
-      </c>
-      <c r="F77" s="22" t="inlineStr">
-        <is>
-          <t>Forensic Engineering: B.E/B.Tech in Mechanical, Civil, Structural or Production Engineering; Physics: M.Sc (1st/2nd class) in Physics, Applied Physics, Material Science, Nuclear Physics, Electronics, Instrumentation, Nano Science/Technology or Geo Physics; Chemistry: M.Sc Chemistry or B.Sc with A.I.C. by examination in Forensic Sciences; Biology: M.Sc (1st/2nd class) in Botany/Zoology/Microbiology/Biochemistry/Genetics/Forensic Science. Exceptionally good eyesight (colour blindness a disqualification) and at least five years practical experience in a Forensic Science, Chemistry, Analytical or Police laboratory</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr">
-        <is>
-          <t>Not stated in the brief notification - the age clause is in the Detailed Notification (due on or before 06/10/2026); left blank rather than guessed</t>
-        </is>
-      </c>
-      <c r="H77" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="I77" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="J77" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K77" s="22" t="inlineStr">
-        <is>
-          <t>06/10/2026 to 27/10/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L77" s="22" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>213 provisional vacancies - SCT PC (Mechanics) (Men), Post Code No. 26: 15; SCT PC (Drivers) (Men), Post Code No. 27: 198</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Post Code 26: SSC plus an ITI certificate in Wireman, Mechanic Motor Vehicle, Mechanic Diesel or Fitter. Post Code 27: Intermediate or its equivalent (or SSC plus an ITI certificate in Auto Electrician, Mechanic Motor Vehicle, Mechanic Diesel or Fitter), and a valid Light Motor Vehicle driving licence held continuously for at least two years as on the date of notification. Men only</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Post Code 26: 18-24 years as on 01/07/2026. Post Code 27: 18-27 years as on 01/07/2026. Serving A.P. Police Home Guards with 360 days of service in the preceding two years get an upper limit of 32 years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service; retrenched State Census Department employees 3 years</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M88" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N88" s="12" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_DRIVERANDMECHANIC_Notification_2026.pdf</t>
+        </is>
+      </c>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="M77" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N77" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O77" s="22" t="inlineStr">
+      <c r="Q88" s="12" t="inlineStr">
+        <is>
+          <t>Detailed notification Rc.No.93/SLPRB/Rect.2/2026 dated 16/09/2026; max age shown is the Post Code 27 limit (Post Code 26 is 18-24); online application and test dates to be notified separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Rc.No.94/SLPRB/Rect.2/2026 - Driver Operator (Men) in State Disaster Response and Fire Services Department</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>147 provisional vacancies - Driver Operator (Men), Post Code No. 43, State Disaster Response and Fire Services Department</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>As on 01/07/2026: Intermediate or its equivalent recognised by the State Government, AND a correct and clear Heavy Transport Vehicle driving licence that has been valid for at least two years as on the date of the notification. Men only</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>18-30 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/1996 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months); retrenched State Census Department temporary employees 3 years</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>To be announced</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>tba</t>
+        </is>
+      </c>
+      <c r="N89" s="12" t="inlineStr">
+        <is>
+          <t>https://slprb.ap.gov.in/2026_PDFS/DRIVER%20OPERATOR%20%20in%20Fire%20Services-%20Notification-%202026.pdf</t>
+        </is>
+      </c>
+      <c r="O89" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="inlineStr">
+        <is>
+          <t>Notification Rc.No.94/SLPRB/Rect.2/2026 dated 17/09/2026 under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026 (147 posts sanctioned); a corrigendum has also been issued; exact online application dates will be notified separately by press release</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Railway Recruitment Boards (Ministry of Railways)</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>CEN No. 09/2026 - Recruitment to Various Posts of Isolated Categories (Ministerial and Isolated Categories)</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>approx. 195 tentative vacancies across all RRBs in Pay Level 2 and Pay Level 7 (post-wise break-up only in the detailed CEN)</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>post-wise, as per the detailed CEN No. 09/2026 (to be published on 05-11-2026)</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>Post-wise, as per the detailed CEN; age to be reckoned as on 01.01.2027 (left blank rather than guessed - the indicative notice states no age limit)</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr"/>
+      <c r="I90" s="12" t="inlineStr"/>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>as per the detailed CEN (SC/ST/OBC-NCL/PwBD/ExSM relaxations)</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="inlineStr">
+        <is>
+          <t>05-11-2026 to 04-12-2026 (tentative, per the indicative notice)</t>
+        </is>
+      </c>
+      <c r="L90" s="12" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="M90" s="12" t="inlineStr">
+        <is>
+          <t>CBT and, where applicable, Performance/Translation Test - dates to be notified</t>
+        </is>
+      </c>
+      <c r="N90" s="12" t="inlineStr">
+        <is>
+          <t>https://www.rrbapply.gov.in</t>
+        </is>
+      </c>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q90" s="12" t="inlineStr">
+        <is>
+          <t>Indicative notice RRB/GHY/Advt./CEN/09/2026 released 21/10/2026; the detailed CEN and the application link open on 05/11/2026. Fee Rs.500 (Rs.250 for SC/ST/PwBD/Female/Transgender/ESM/Minority/EBC, refundable after appearing in CBT-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Junior Engineer (Civil, Mechanical and Electrical) Examination, 2026 (SSC JE) including Scientific Assistant and JE (Telecommunication)</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>1699 vacancies - Junior Engineer (Civil/Mechanical/Electrical), Scientific Assistant (IMD) and JE (Telecommunication), across 13 departments</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Degree or Diploma in the relevant engineering discipline (post-wise), or B.Sc./M.Sc. for Scientific Assistant</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>18 to 30 years (age reckoned as on 01-08-2026)</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>SC/ST 5 years; OBC 3 years; PwBD 10 years (13/15 years for OBC and SC/ST PwBD); Ex-servicemen as per notice</t>
+        </is>
+      </c>
+      <c r="K91" s="12" t="inlineStr">
+        <is>
+          <t>02-09-2026 to 22-09-2026 (fee payment up to 23-09-2026; correction 28-09-2026 to 30-09-2026)</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>Paper-I 02-11-2026 to 06-11-2026; JE (Telecommunication) 30-11-2026 to 01-12-2026</t>
+        </is>
+      </c>
+      <c r="N91" s="12" t="inlineStr">
+        <is>
+          <t>https://ssc.gov.in</t>
+        </is>
+      </c>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q91" s="12" t="inlineStr">
+        <is>
+          <t>Applications closed 22/09/2026. Exam-city details released 23/10/2026; admission certificates 2-3 days before each candidate's paper. Paper-I is now only qualifying - the merit list is prepared on Paper-II marks. Own-scribe OTR mapping and subject-preference changes closed 27/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Central Govt</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Sub-Inspector in Delhi Police and Central Armed Police Forces Examination, 2026 (SSC CPO)</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>1871 tentative vacancies - SI (Executive) in Delhi Police (Male 205, Female 112), SI (GD) in CAPFs 1320 and SI (Fire) in CISF (Male) 234</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in any discipline from a recognised university</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr"/>
+      <c r="I92" s="12" t="inlineStr"/>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>as per the notice (SC/ST/OBC/EWS/ExSM/PwBD relaxations)</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>10-09-2026 to 30-09-2026 (fee payment up to 01-10-2026; correction 08-10-2026 to 10-10-2026)</t>
+        </is>
+      </c>
+      <c r="L92" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="M92" s="12" t="inlineStr">
+        <is>
+          <t>Paper-I (CBE) 23-11-2026 to 28-11-2026 (revised from 20-28 November by corrigendum dated 26-10-2026); PET/PST and Paper-II to be notified</t>
+        </is>
+      </c>
+      <c r="N92" s="12" t="inlineStr">
+        <is>
+          <t>https://ssc.gov.in</t>
+        </is>
+      </c>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q92" s="12" t="inlineStr">
+        <is>
+          <t>Applications closed 30/09/2026. 2026 cycle introduced a revised pattern for Paper-I and Paper-II and added SI (Fire) Male in CISF. Paper-I dates revised by the corrigendum of 26/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>High Court of Andhra Pradesh, Amaravati</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Recruitment of District Judge through Limited Departmental Competitive Examination (LDCE), 2026 - 30 posts</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>30 posts of District Judge, filled by LDCE among Civil Judges (Senior Division)</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Civil Judge (Senior Division) in the A.P. State Judicial Service, as prescribed in the notification dated 30-09-2026</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>not stated in sources consulted</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr"/>
+      <c r="I93" s="12" t="inlineStr"/>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>as per the notification</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>30-09-2026 to 10-11-2026 (extended from 26-10-2026)</t>
+        </is>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>to be notified</t>
+        </is>
+      </c>
+      <c r="N93" s="12" t="inlineStr">
+        <is>
+          <t>https://aphc.gov.in/recruitment.php</t>
+        </is>
+      </c>
+      <c r="O93" s="12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P77" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Q77" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 15/09/2026; applications 06/10/2026 to 27/10/2026 (11:59 PM). The detailed notification had still not been hosted as on 27/10/2026, so the age clause is left blank - check the Commission's site before the window closes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C78" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 29/2026 - Deputy Commissioner of Endowments and Assistant Commissioner of Endowments, A.P. Charitable and Hindu Religious Institutions and Endowments Service</t>
-        </is>
-      </c>
-      <c r="D78" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E78" s="22" t="inlineStr">
-        <is>
-          <t>11 posts (Deputy Commissioner of Endowments 6 - Rs 65,360-1,54,980; Assistant Commissioner of Endowments 5 - Rs 48,440-1,37,220)</t>
-        </is>
-      </c>
-      <c r="F78" s="22" t="inlineStr">
-        <is>
-          <t>Practising advocate - Deputy Commissioner: at least 5 years' practice in the High Court of A.P. or the Supreme Court; Assistant Commissioner: advocate of the A.P. High Court for at least 3 years. Candidates must profess the Hindu religion (s.29(3), AP Charitable and Hindu Religious Institutions and Endowments Act, 1987)</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t>28-44 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H78" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="I78" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J78" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K78" s="22" t="inlineStr">
-        <is>
-          <t>02/11/2026 to 22/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L78" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="M78" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N78" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O78" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P78" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q78" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 02/11/2026; BC-C and BC-E candidates are not eligible to the Endowments posts under the department special rules; detailed notification due on or before 02/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 31/2026 - Assistant Director (Mines), A.P. Mines and Geology Service</t>
-        </is>
-      </c>
-      <c r="D79" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
-        <is>
-          <t>1 provisional vacancy - Assistant Director (Mines), pay Rs 57,100 - 1,47,760</t>
-        </is>
-      </c>
-      <c r="F79" s="22" t="inlineStr">
-        <is>
-          <t>Degree in Mining Engineering from a recognised university, or Diploma in Mining Engineering from Indian School of Mines, Dhanbad or equivalent</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr">
-        <is>
-          <t>18-44 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H79" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="I79" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J79" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K79" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L79" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M79" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N79" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O79" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P79" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q79" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026 and is the crucial date for eligibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C80" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 32/2026 - Technical Assistant, A.P. Mines and Geology Sub-Service</t>
-        </is>
-      </c>
-      <c r="D80" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E80" s="22" t="inlineStr">
-        <is>
-          <t>36 provisional vacancies - Technical Assistant in A.P. Mines and Geology Sub-Service, pay Rs 35,570 - 1,09,910</t>
-        </is>
-      </c>
-      <c r="F80" s="22" t="inlineStr">
-        <is>
-          <t>B.Sc degree in Geology from a recognised university; practical experience of not less than one year in investigation of mineral deposits, geological mapping, mining or underground water resources preferred</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t>18-44 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H80" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="I80" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J80" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K80" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L80" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M80" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N80" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O80" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P80" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q80" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 33/2026 - Royalty Inspector, A.P. Mines and Geology Service</t>
-        </is>
-      </c>
-      <c r="D81" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E81" s="22" t="inlineStr">
-        <is>
-          <t>9 provisional vacancies - Royalty Inspector, pay Rs 45,830 - 1,30,580</t>
-        </is>
-      </c>
-      <c r="F81" s="22" t="inlineStr">
-        <is>
-          <t>Educational qualification will be given in the Detailed Notification, due on or before 06/11/2026</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr">
-        <is>
-          <t>18-44 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J81" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K81" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L81" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M81" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N81" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O81" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P81" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q81" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; qualification and community break-up to be published in the detailed notification</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 34/2026 - Lab Assistant, A.P. Mining Subordinate Service</t>
-        </is>
-      </c>
-      <c r="D82" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E82" s="22" t="inlineStr">
-        <is>
-          <t>1 provisional vacancy - Lab Assistant in A.P. Mining Subordinate Service, pay Rs 35,570 - 1,09,910</t>
-        </is>
-      </c>
-      <c r="F82" s="22" t="inlineStr">
-        <is>
-          <t>B.Sc degree with Chemistry from a university recognised by the UGC</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t>The brief notification fixes only the age reckoning date (01/07/2026) and defers the age range to the Detailed Notification - left blank rather than guessed</t>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="I82" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="J82" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K82" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L82" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M82" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N82" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O82" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P82" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Q82" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026. The detailed notification is still not published as on 27/10/2026 - the brief notification states it will be available on or before 06/11/2026, so the age range remains blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B83" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C83" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 35/2026 - Assistant Chemical Examiner, A.P. Prohibition and Excise Subordinate Service</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E83" s="22" t="inlineStr">
-        <is>
-          <t>9 provisional vacancies - Assistant Chemical Examiner, pay Rs 40,970 - 1,24,380</t>
-        </is>
-      </c>
-      <c r="F83" s="22" t="inlineStr">
-        <is>
-          <t>Bachelor's Degree in Science with Chemistry, or B.Sc (Pharmacy), from a recognised university or equivalent</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr">
-        <is>
-          <t>18-44 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H83" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="I83" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J83" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K83" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L83" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M83" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N83" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O83" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P83" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q83" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; detailed notification due on or before 06/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh Public Service Commission (APPSC)</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="inlineStr">
-        <is>
-          <t>Notification No. 36/2026 - Assistant Motor Vehicle Inspector, A.P. Transport Service</t>
-        </is>
-      </c>
-      <c r="D84" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E84" s="22" t="inlineStr">
-        <is>
-          <t>50 provisional vacancies - Assistant Motor Vehicle Inspector, pay Rs 48,440 - 1,37,220</t>
-        </is>
-      </c>
-      <c r="F84" s="22" t="inlineStr">
-        <is>
-          <t>Degree in Mechanical or Automobile Engineering, OR Diploma in Automobile Engineering from SBTET Andhra Pradesh / Technological Diploma Examination Board Hyderabad or equivalent; plus a motor driving licence with at least 3 years driving experience and a Heavy Transport Vehicle endorsement (2 years accepted where 3-year candidates are unavailable). Women holding only an LMV licence must acquire the HTV endorsement within two years of joining</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t>21-36 years (Age as on 01/07/2026)</t>
-        </is>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="J84" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST/BC/EWS 5 years; PwBD 10 years; ex-servicemen and regular AP Government employees as per A.P. State and Subordinate Service Rules (relaxation details in the Detailed Notification)</t>
-        </is>
-      </c>
-      <c r="K84" s="22" t="inlineStr">
-        <is>
-          <t>06/11/2026 to 26/11/2026 (11:59 PM)</t>
-        </is>
-      </c>
-      <c r="L84" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="M84" s="22" t="inlineStr">
-        <is>
-          <t>tba (single-level CBRT, no screening test)</t>
-        </is>
-      </c>
-      <c r="N84" s="22" t="inlineStr">
-        <is>
-          <t>https://psc.ap.gov.in</t>
-        </is>
-      </c>
-      <c r="O84" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P84" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q84" s="22" t="inlineStr">
-        <is>
-          <t>Brief notification dated 13/10/2026; applications open 06/11/2026; physical requirements and community break-up to be given in the detailed notification due on or before 06/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>Central Govt</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="inlineStr">
-        <is>
-          <t>NTA (for the Department of Higher Education, Ministry of Education)</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="inlineStr">
-        <is>
-          <t>Joint Entrance Examination (Main) - 2027, Session 1 (January 2027)</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>entrance-exam</t>
-        </is>
-      </c>
-      <c r="E85" s="22" t="inlineStr">
-        <is>
-          <t>Paper 1 (B.E./B.Tech) and Paper 2A (B.Arch) / 2B (B.Planning) - admission to NITs, IIITs and other centrally funded technical institutions, and the eligibility test for JEE (Advanced)</t>
-        </is>
-      </c>
-      <c r="F85" s="22" t="inlineStr">
-        <is>
-          <t>Pass in Class 12 (or equivalent) as per the JEE (Main) 2027 Information Bulletin - eligibility is fixed by the year of passing the qualifying examination</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr">
-        <is>
-          <t>No age range is prescribed in the public notice - eligibility for JEE (Main) 2027 is determined by the year of passing the Class 12 qualifying examination, so no numeric age limit is shown</t>
-        </is>
-      </c>
-      <c r="H85" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="I85" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="J85" s="22" t="inlineStr">
-        <is>
-          <t>Not applicable - no age limit prescribed</t>
-        </is>
-      </c>
-      <c r="K85" s="22" t="inlineStr">
-        <is>
-          <t>24/10/2026 to 22/11/2026 (11:50 PM); late fee window 23/11/2026 to 26/11/2026; correction in particulars 27/11/2026 to 29/11/2026</t>
-        </is>
-      </c>
-      <c r="L85" s="22" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="M85" s="22" t="inlineStr">
-        <is>
-          <t>20, 21, 22, 23, 24 and 28 January 2027 (Session 1); city intimation slip 30/12/2026, admit cards from 13/01/2027</t>
-        </is>
-      </c>
-      <c r="N85" s="22" t="inlineStr">
-        <is>
-          <t>https://jeemain.nta.nic.in/</t>
-        </is>
-      </c>
-      <c r="O85" s="22" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P85" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q85" s="22" t="inlineStr">
-        <is>
-          <t>Public notice dated 24/10/2026; Session 2 (April 2027) applications run 05/01/2027 to 03/02/2027 under a separate notice; the exam is held in 13 languages including Telugu; one application only per candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="22" t="inlineStr">
-        <is>
-          <t>Central Govt</t>
-        </is>
-      </c>
-      <c r="B86" s="22" t="inlineStr">
-        <is>
-          <t>UPSC</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="inlineStr">
-        <is>
-          <t>Special Advertisement No. 51/2026 - Principal and Vice-Principal, Education Department, Government of NCT of Delhi</t>
-        </is>
-      </c>
-      <c r="D86" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E86" s="22" t="inlineStr">
-        <is>
-          <t>828 posts (Principal 124 - UR 69, EWS 11, OBC 18, SC 16, ST 10; Vice-Principal 704 - UR 287, EWS 71, OBC 189, SC 103, ST 54)</t>
-        </is>
-      </c>
-      <c r="F86" s="22" t="inlineStr">
-        <is>
-          <t>Master's Degree and Bachelor of Education from a recognised university/institute. Principal: ten years' teaching experience as Vice-Principal/PGT/TGT in a recognised high/higher secondary school or college. Vice-Principal: two years as PGT or three years as TGT. Doctorate and administrative charge desirable</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t>Principal: 50 years for UR/EWS, 53 years for OBC and 55 years for SC/ST. Vice-Principal: 35 years for UR/EWS, 38 years for OBC and 40 years for SC/ST. Relaxable up to 10 years for PwBD subject to a maximum of 56 years</t>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>55</v>
-      </c>
-      <c r="J86" s="22" t="inlineStr">
-        <is>
-          <t>SC/ST 5 years; OBC 3 years; PwBD up to 10 years (maximum age 56); OBC reservation only against a certificate issued by the Government of NCT of Delhi</t>
-        </is>
-      </c>
-      <c r="K86" s="22" t="inlineStr">
-        <is>
-          <t>25/07/2026 to 14/08/2026, extended to 17/08/2026 (18:00 hrs); crucial date for age and eligibility remained 14/08/2026</t>
-        </is>
-      </c>
-      <c r="L86" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="M86" s="22" t="inlineStr">
-        <is>
-          <t>Pen-and-paper Combined Recruitment Test (CRT) on 01/11/2026 for shortlisting, followed by interview</t>
-        </is>
-      </c>
-      <c r="N86" s="22" t="inlineStr">
-        <is>
-          <t>https://www.upsc.gov.in/sites/default/files/AdvtNo-51-2026-Special-Engl-240726.pdf</t>
-        </is>
-      </c>
-      <c r="O86" s="22" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="P86" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="Q86" s="22" t="inlineStr">
-        <is>
-          <t>Applications closed 17/08/2026; the shortlisting CRT is scheduled for 01/11/2026, so admit-card and exam-city notices are the live items to watch; max age shown is the Principal UR/EWS limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
-        </is>
-      </c>
-      <c r="C87" s="22" t="inlineStr">
-        <is>
-          <t>Rc.No.92/SLPRB/Rect.2/2026 - SCT Police Constables (Communications) (Men and Women)</t>
-        </is>
-      </c>
-      <c r="D87" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E87" s="22" t="inlineStr">
-        <is>
-          <t>200 provisional vacancies - Stipendiary Cadet Trainee Police Constable (Communications), Post Code No. 25</t>
-        </is>
-      </c>
-      <c r="F87" s="22" t="inlineStr">
-        <is>
-          <t>As on 01/07/2026: SSC plus an ITI certificate in Electronic Mechanic, Information Technology and Electronic System Maintenance, Computer Operator and Programming Assistant, Mechanic Consumer Electronics or Electrician; OR two-year Intermediate with MPC, or vocational Intermediate in EET (Electronic Engineering Technician) / ET (Electrical Technician) after SSC</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr">
-        <is>
-          <t>18-24 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/2002 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
-        </is>
-      </c>
-      <c r="H87" s="22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I87" s="22" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J87" s="22" t="inlineStr">
-        <is>
-          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months as instructor); retrenched State Census Department temporary employees 3 years</t>
-        </is>
-      </c>
-      <c r="K87" s="22" t="inlineStr">
-        <is>
-          <t>To be announced</t>
-        </is>
-      </c>
-      <c r="L87" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="M87" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="N87" s="22" t="inlineStr">
-        <is>
-          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_COMM_Notification_2026.pdf</t>
-        </is>
-      </c>
-      <c r="O87" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P87" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Q87" s="22" t="inlineStr">
-        <is>
-          <t>Detailed notification Rc.No.92/SLPRB/Rect.2/2026 dated 16/09/2026 issued under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026; online application and Preliminary Written Test dates to be notified separately by press release</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B88" s="22" t="inlineStr">
-        <is>
-          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="inlineStr">
-        <is>
-          <t>Rc.No.93/SLPRB/Rect.2/2026 - SCT Police Constables (Mechanics) and (Drivers), Police Transport Organisation</t>
-        </is>
-      </c>
-      <c r="D88" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E88" s="22" t="inlineStr">
-        <is>
-          <t>213 provisional vacancies - SCT PC (Mechanics) (Men), Post Code No. 26: 15; SCT PC (Drivers) (Men), Post Code No. 27: 198</t>
-        </is>
-      </c>
-      <c r="F88" s="22" t="inlineStr">
-        <is>
-          <t>Post Code 26: SSC plus an ITI certificate in Wireman, Mechanic Motor Vehicle, Mechanic Diesel or Fitter. Post Code 27: Intermediate or its equivalent (or SSC plus an ITI certificate in Auto Electrician, Mechanic Motor Vehicle, Mechanic Diesel or Fitter), and a valid Light Motor Vehicle driving licence held continuously for at least two years as on the date of notification. Men only</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t>Post Code 26: 18-24 years as on 01/07/2026. Post Code 27: 18-27 years as on 01/07/2026. Serving A.P. Police Home Guards with 360 days of service in the preceding two years get an upper limit of 32 years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I88" s="22" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J88" s="22" t="inlineStr">
-        <is>
-          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service; retrenched State Census Department employees 3 years</t>
-        </is>
-      </c>
-      <c r="K88" s="22" t="inlineStr">
-        <is>
-          <t>To be announced</t>
-        </is>
-      </c>
-      <c r="L88" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="M88" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="N88" s="22" t="inlineStr">
-        <is>
-          <t>https://slprb.ap.gov.in/2026_PDFS/SLPRB_AP_PC_DRIVERANDMECHANIC_Notification_2026.pdf</t>
-        </is>
-      </c>
-      <c r="O88" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P88" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Q88" s="22" t="inlineStr">
-        <is>
-          <t>Detailed notification Rc.No.93/SLPRB/Rect.2/2026 dated 16/09/2026; max age shown is the Post Code 27 limit (Post Code 26 is 18-24); online application and test dates to be notified separately</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="22" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>State Level Police Recruitment Board, Andhra Pradesh (SLPRB AP)</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="inlineStr">
-        <is>
-          <t>Rc.No.94/SLPRB/Rect.2/2026 - Driver Operator (Men) in State Disaster Response and Fire Services Department</t>
-        </is>
-      </c>
-      <c r="D89" s="22" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="E89" s="22" t="inlineStr">
-        <is>
-          <t>147 provisional vacancies - Driver Operator (Men), Post Code No. 43, State Disaster Response and Fire Services Department</t>
-        </is>
-      </c>
-      <c r="F89" s="22" t="inlineStr">
-        <is>
-          <t>As on 01/07/2026: Intermediate or its equivalent recognised by the State Government, AND a correct and clear Heavy Transport Vehicle driving licence that has been valid for at least two years as on the date of the notification. Men only</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr">
-        <is>
-          <t>18-30 years as on 01/07/2026 for all other candidates (born not earlier than 02/07/1996 and not later than 01/07/2008); 18-32 years as on 01/07/2026 for serving A.P. Police Home Guards with at least 360 days of service in the preceding two years (born not earlier than 02/07/1994 and not later than 01/07/2008)</t>
-        </is>
-      </c>
-      <c r="H89" s="22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I89" s="22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J89" s="22" t="inlineStr">
-        <is>
-          <t>EWS 5 years; BC (Non-Creamy Layer) / SC / ST 5 years; A.P. State Government employees up to 5 years (length of regular service; APTRANSCO/Discoms/APGENCO/corporations/municipalities excluded); Armed Forces service 3 years plus length of service; whole-time NCC instructors 3 years plus service (minimum 6 months); retrenched State Census Department temporary employees 3 years</t>
-        </is>
-      </c>
-      <c r="K89" s="22" t="inlineStr">
-        <is>
-          <t>To be announced</t>
-        </is>
-      </c>
-      <c r="L89" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="M89" s="22" t="inlineStr">
-        <is>
-          <t>tba</t>
-        </is>
-      </c>
-      <c r="N89" s="22" t="inlineStr">
-        <is>
-          <t>https://slprb.ap.gov.in/2026_PDFS/DRIVER%20OPERATOR%20%20in%20Fire%20Services-%20Notification-%202026.pdf</t>
-        </is>
-      </c>
-      <c r="O89" s="22" t="inlineStr">
-        <is>
-          <t>upcoming</t>
-        </is>
-      </c>
-      <c r="P89" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Q89" s="22" t="inlineStr">
-        <is>
-          <t>Notification Rc.No.94/SLPRB/Rect.2/2026 dated 17/09/2026 under G.O.Ms.No.81, Finance (HR-I) Department, dated 22/08/2026 (147 posts sanctioned); a corrigendum has also been issued; exact online application dates will be notified separately by press release</t>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="inlineStr">
+        <is>
+          <t>Notification issued 30/09/2026; the High Court extended the last date for submission of filled-in applications to 10/11/2026 by notice dated 17/10/2026. Open only to in-service Civil Judges (Senior Division) - not a direct-recruitment post.</t>
         </is>
       </c>
     </row>
